--- a/schedule_test (1).xlsx
+++ b/schedule_test (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Downloads\team-ENERGO-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A40E0C-C830-4FC5-B331-5D6FA638C847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45C3FE4-0078-4B33-B699-44A9B5A7ACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
   <si>
     <t>День</t>
   </si>
@@ -149,21 +149,6 @@
   </si>
   <si>
     <t>Пятница</t>
-  </si>
-  <si>
-    <t>Суббота</t>
-  </si>
-  <si>
-    <t>9:00-10:30</t>
-  </si>
-  <si>
-    <t>Физическая культура</t>
-  </si>
-  <si>
-    <t>Джаксыбеков Т.</t>
-  </si>
-  <si>
-    <t>Спортзал</t>
   </si>
   <si>
     <t>192.168.1.3</t>
@@ -720,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3">
         <v>554</v>
@@ -732,7 +717,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1022,21 +1007,11 @@
       <c r="J16" s="14"/>
     </row>
     <row r="17" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="16"/>

--- a/schedule_test (1).xlsx
+++ b/schedule_test (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Downloads\team-ENERGO-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45C3FE4-0078-4B33-B699-44A9B5A7ACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B913EDF-5EC8-43C4-AF98-C55DF908F87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>День</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>Camera_B201</t>
+  </si>
+  <si>
+    <t>Вместимость</t>
   </si>
 </sst>
 </file>
@@ -612,19 +615,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,23 +644,26 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -672,23 +679,26 @@
       <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4">
+        <v>20</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>554</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -704,23 +714,26 @@
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>554</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -736,13 +749,16 @@
       <c r="E4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4">
+        <v>20</v>
+      </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
@@ -758,13 +774,16 @@
       <c r="E5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="8">
+        <v>30</v>
+      </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
@@ -780,13 +799,16 @@
       <c r="E6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="8">
+        <v>15</v>
+      </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
@@ -802,13 +824,16 @@
       <c r="E7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8">
+        <v>34</v>
+      </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>34</v>
       </c>
@@ -824,13 +849,16 @@
       <c r="E8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="10">
+        <v>25</v>
+      </c>
       <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="9"/>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>34</v>
       </c>
@@ -846,13 +874,16 @@
       <c r="E9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="10">
+        <v>16</v>
+      </c>
       <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="H9" s="9"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>34</v>
       </c>
@@ -868,13 +899,16 @@
       <c r="E10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="10">
+        <v>18</v>
+      </c>
       <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="H10" s="9"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
@@ -890,13 +924,16 @@
       <c r="E11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="12">
+        <v>23</v>
+      </c>
       <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-    </row>
-    <row r="12" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>38</v>
       </c>
@@ -912,13 +949,16 @@
       <c r="E12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="12">
+        <v>15</v>
+      </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="12"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>38</v>
       </c>
@@ -934,13 +974,16 @@
       <c r="E13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="12">
+        <v>38</v>
+      </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="12"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>42</v>
       </c>
@@ -956,13 +999,16 @@
       <c r="E14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="14">
+        <v>41</v>
+      </c>
       <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
+      <c r="H14" s="13"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>42</v>
       </c>
@@ -978,13 +1024,16 @@
       <c r="E15" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="13"/>
+      <c r="F15" s="14">
+        <v>36</v>
+      </c>
       <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
+      <c r="H15" s="13"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>42</v>
       </c>
@@ -1000,23 +1049,27 @@
       <c r="E16" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="14">
+        <v>67</v>
+      </c>
       <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
